--- a/diseases/d234/1995-1999.xlsx
+++ b/diseases/d234/1995-1999.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29667,7 +29667,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35691,7 +35691,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36630,7 +36630,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39447,7 +39447,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41325,7 +41325,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42264,7 +42264,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43593,7 +43593,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45471,7 +45471,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -46410,7 +46410,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47349,7 +47349,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -48288,7 +48288,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49227,7 +49227,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51105,7 +51105,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -52044,7 +52044,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -52983,7 +52983,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -53922,7 +53922,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">

--- a/diseases/d234/1995-1999.xlsx
+++ b/diseases/d234/1995-1999.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21216,7 +21216,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25911,7 +25911,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29667,7 +29667,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33813,7 +33813,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35691,7 +35691,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -36630,7 +36630,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38508,7 +38508,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39447,7 +39447,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41325,7 +41325,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42264,7 +42264,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43593,7 +43593,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN226" t="b">
@@ -44532,7 +44532,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45471,7 +45471,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -46410,7 +46410,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47349,7 +47349,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -48288,7 +48288,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49227,7 +49227,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -50166,7 +50166,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51105,7 +51105,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -52044,7 +52044,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -52983,7 +52983,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -53922,7 +53922,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">

--- a/diseases/d234/1995-1999.xlsx
+++ b/diseases/d234/1995-1999.xlsx
@@ -19878,6 +19878,11 @@
       <c r="Q100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -19895,7 +19900,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -19905,6 +19915,11 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -20802,6 +20817,11 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -20819,7 +20839,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -20829,6 +20854,11 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -21726,6 +21756,11 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -21743,7 +21778,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -21753,6 +21793,11 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -22650,6 +22695,11 @@
       <c r="Q115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -22667,7 +22717,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -22677,6 +22732,11 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -23574,6 +23634,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -23591,7 +23656,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -23601,6 +23671,11 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -24498,6 +24573,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -24515,7 +24595,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -24525,6 +24610,11 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -25422,6 +25512,11 @@
       <c r="Q130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -25439,7 +25534,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -25449,6 +25549,11 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -26346,6 +26451,11 @@
       <c r="Q135" t="n">
         <v>0</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -26363,7 +26473,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -26373,6 +26488,11 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -27270,6 +27390,11 @@
       <c r="Q140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -27287,7 +27412,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -27297,6 +27427,11 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -28194,6 +28329,11 @@
       <c r="Q145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -28211,7 +28351,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -28221,6 +28366,11 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -29118,6 +29268,11 @@
       <c r="Q150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -29135,7 +29290,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
@@ -29145,6 +29305,11 @@
       </c>
       <c r="AT150" t="n">
         <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -30042,6 +30207,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -30059,7 +30229,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
@@ -30069,6 +30244,11 @@
       </c>
       <c r="AT155" t="n">
         <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -31356,6 +31536,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -31373,7 +31558,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -31383,6 +31573,11 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -32280,6 +32475,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -32297,7 +32497,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -32307,6 +32512,11 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -33204,6 +33414,11 @@
       <c r="Q172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -33221,7 +33436,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
@@ -33231,6 +33451,11 @@
       </c>
       <c r="AT172" t="n">
         <v>1</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -34128,6 +34353,11 @@
       <c r="Q177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -34145,7 +34375,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
@@ -34155,6 +34390,11 @@
       </c>
       <c r="AT177" t="n">
         <v>1</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -35052,6 +35292,11 @@
       <c r="Q182" t="n">
         <v>0</v>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -35069,7 +35314,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
@@ -35079,6 +35329,11 @@
       </c>
       <c r="AT182" t="n">
         <v>1</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -35976,6 +36231,11 @@
       <c r="Q187" t="n">
         <v>0</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -35993,7 +36253,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
@@ -36003,6 +36268,11 @@
       </c>
       <c r="AT187" t="n">
         <v>1</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -36900,6 +37170,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -36917,7 +37192,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
@@ -36927,6 +37207,11 @@
       </c>
       <c r="AT192" t="n">
         <v>1</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -37824,6 +38109,11 @@
       <c r="Q197" t="n">
         <v>0</v>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -37841,7 +38131,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
@@ -37851,6 +38146,11 @@
       </c>
       <c r="AT197" t="n">
         <v>1</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -38748,6 +39048,11 @@
       <c r="Q202" t="n">
         <v>0</v>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -38765,7 +39070,12 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
@@ -38775,6 +39085,11 @@
       </c>
       <c r="AT202" t="n">
         <v>1</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -39672,6 +39987,11 @@
       <c r="Q207" t="n">
         <v>0</v>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U207" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -39689,7 +40009,12 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
@@ -39699,6 +40024,11 @@
       </c>
       <c r="AT207" t="n">
         <v>1</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -40596,6 +40926,11 @@
       <c r="Q212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -40613,7 +40948,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
@@ -40623,6 +40963,11 @@
       </c>
       <c r="AT212" t="n">
         <v>1</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -41520,6 +41865,11 @@
       <c r="Q217" t="n">
         <v>0</v>
       </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -41537,7 +41887,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
@@ -41547,6 +41902,11 @@
       </c>
       <c r="AT217" t="n">
         <v>1</v>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -42834,6 +43194,11 @@
       <c r="Q224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -42851,7 +43216,12 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
@@ -42861,6 +43231,11 @@
       </c>
       <c r="AT224" t="n">
         <v>1</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -43758,6 +44133,11 @@
       <c r="Q229" t="n">
         <v>0</v>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U229" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -43775,7 +44155,12 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
@@ -43785,6 +44170,11 @@
       </c>
       <c r="AT229" t="n">
         <v>1</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -44682,6 +45072,11 @@
       <c r="Q234" t="n">
         <v>0</v>
       </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U234" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -44699,7 +45094,12 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
@@ -44709,6 +45109,11 @@
       </c>
       <c r="AT234" t="n">
         <v>1</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
@@ -45606,6 +46011,11 @@
       <c r="Q239" t="n">
         <v>0</v>
       </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U239" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -45623,7 +46033,12 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
@@ -45633,6 +46048,11 @@
       </c>
       <c r="AT239" t="n">
         <v>1</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
@@ -46530,6 +46950,11 @@
       <c r="Q244" t="n">
         <v>0</v>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U244" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -46547,7 +46972,12 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
@@ -46557,6 +46987,11 @@
       </c>
       <c r="AT244" t="n">
         <v>1</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -47454,6 +47889,11 @@
       <c r="Q249" t="n">
         <v>0</v>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -47471,7 +47911,12 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
@@ -47481,6 +47926,11 @@
       </c>
       <c r="AT249" t="n">
         <v>1</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -48378,6 +48828,11 @@
       <c r="Q254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U254" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -48395,7 +48850,12 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
@@ -48405,6 +48865,11 @@
       </c>
       <c r="AT254" t="n">
         <v>1</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -49302,6 +49767,11 @@
       <c r="Q259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U259" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -49319,7 +49789,12 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
@@ -49329,6 +49804,11 @@
       </c>
       <c r="AT259" t="n">
         <v>1</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -50226,6 +50706,11 @@
       <c r="Q264" t="n">
         <v>0</v>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U264" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -50243,7 +50728,12 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr">
@@ -50253,6 +50743,11 @@
       </c>
       <c r="AT264" t="n">
         <v>1</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -51150,6 +51645,11 @@
       <c r="Q269" t="n">
         <v>0</v>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -51167,7 +51667,12 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr">
@@ -51177,6 +51682,11 @@
       </c>
       <c r="AT269" t="n">
         <v>1</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
@@ -52074,6 +52584,11 @@
       <c r="Q274" t="n">
         <v>0</v>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U274" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -52091,7 +52606,12 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr">
@@ -52101,6 +52621,11 @@
       </c>
       <c r="AT274" t="n">
         <v>1</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
@@ -52998,6 +53523,11 @@
       <c r="Q279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>SER_HK_PARATYPHOID_MONTHLY</t>
@@ -53015,7 +53545,12 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr">
@@ -53025,6 +53560,11 @@
       </c>
       <c r="AT279" t="n">
         <v>1</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
